--- a/rcads/data/xls/10_Instruments.xlsx
+++ b/rcads/data/xls/10_Instruments.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_10_Instruments"/>
   </sheets>
   <definedNames>
-    <definedName name="_10_Instruments">'_10_Instruments'!$A$1:$J$170</definedName>
+    <definedName name="_10_Instruments">'_10_Instruments'!$A$1:$J$176</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J170"/>
+  <dimension ref="A1:J176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -420,7 +420,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="0" t="b">
         <v>0</v>
@@ -451,7 +451,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="0" t="b">
         <v>0</v>
@@ -482,7 +482,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="0" t="b">
         <v>0</v>
@@ -513,7 +513,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="0" t="b">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="0" t="b">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="0" t="b">
         <v>0</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="0" t="b">
         <v>0</v>
@@ -637,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="0" t="b">
         <v>0</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="0" t="b">
         <v>0</v>
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="0" t="b">
         <v>0</v>
@@ -730,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="0" t="b">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="0" t="b">
         <v>0</v>
@@ -5354,13 +5354,8 @@
       <c r="E155" s="0">
         <v>1</v>
       </c>
-      <c r="F155" s="0" t="inlineStr">
-        <is>
-          <t>needs to be entered</t>
-        </is>
-      </c>
       <c r="G155" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" s="0" t="b">
         <v>0</v>
@@ -5390,13 +5385,8 @@
       <c r="E156" s="0">
         <v>2</v>
       </c>
-      <c r="F156" s="0" t="inlineStr">
-        <is>
-          <t>needs to be entered</t>
-        </is>
-      </c>
       <c r="G156" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" s="0" t="b">
         <v>0</v>
@@ -5435,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="H157" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I157" s="0" t="b">
         <v>0</v>
@@ -5471,7 +5461,7 @@
         <v>1</v>
       </c>
       <c r="H158" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158" s="0" t="b">
         <v>0</v>
@@ -5507,7 +5497,7 @@
         <v>1</v>
       </c>
       <c r="H159" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I159" s="0" t="b">
         <v>0</v>
@@ -5543,7 +5533,7 @@
         <v>1</v>
       </c>
       <c r="H160" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" s="0" t="b">
         <v>0</v>
@@ -5579,7 +5569,7 @@
         <v>1</v>
       </c>
       <c r="H161" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" s="0" t="b">
         <v>0</v>
@@ -5615,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="H162" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" s="0" t="b">
         <v>0</v>
@@ -5869,6 +5859,192 @@
         <v>0</v>
       </c>
       <c r="J170" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="171">
+      <c r="A171" s="0">
+        <v>170</v>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-Y-IT</t>
+        </is>
+      </c>
+      <c r="C171" s="0">
+        <v>1</v>
+      </c>
+      <c r="D171" s="0">
+        <v>36</v>
+      </c>
+      <c r="E171" s="0">
+        <v>1</v>
+      </c>
+      <c r="G171" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H171" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I171" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J171" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="172">
+      <c r="A172" s="0">
+        <v>171</v>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-CG-IT</t>
+        </is>
+      </c>
+      <c r="C172" s="0">
+        <v>1</v>
+      </c>
+      <c r="D172" s="0">
+        <v>36</v>
+      </c>
+      <c r="E172" s="0">
+        <v>2</v>
+      </c>
+      <c r="G172" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H172" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I172" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J172" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="173">
+      <c r="A173" s="0">
+        <v>172</v>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-47-Y-ZU</t>
+        </is>
+      </c>
+      <c r="C173" s="0">
+        <v>1</v>
+      </c>
+      <c r="D173" s="0">
+        <v>41</v>
+      </c>
+      <c r="E173" s="0">
+        <v>1</v>
+      </c>
+      <c r="G173" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H173" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I173" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J173" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="174">
+      <c r="A174" s="0">
+        <v>173</v>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-47-CG-ZU</t>
+        </is>
+      </c>
+      <c r="C174" s="0">
+        <v>1</v>
+      </c>
+      <c r="D174" s="0">
+        <v>41</v>
+      </c>
+      <c r="E174" s="0">
+        <v>2</v>
+      </c>
+      <c r="G174" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H174" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I174" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J174" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="175">
+      <c r="A175" s="0">
+        <v>174</v>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-Y-ZU</t>
+        </is>
+      </c>
+      <c r="C175" s="0">
+        <v>1</v>
+      </c>
+      <c r="D175" s="0">
+        <v>41</v>
+      </c>
+      <c r="E175" s="0">
+        <v>1</v>
+      </c>
+      <c r="G175" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H175" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I175" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J175" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="176">
+      <c r="A176" s="0">
+        <v>175</v>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-CG-ZU</t>
+        </is>
+      </c>
+      <c r="C176" s="0">
+        <v>1</v>
+      </c>
+      <c r="D176" s="0">
+        <v>41</v>
+      </c>
+      <c r="E176" s="0">
+        <v>2</v>
+      </c>
+      <c r="G176" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H176" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I176" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J176" s="0" t="b">
         <v>0</v>
       </c>
     </row>

--- a/rcads/data/xls/10_Instruments.xlsx
+++ b/rcads/data/xls/10_Instruments.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_10_Instruments"/>
   </sheets>
   <definedNames>
-    <definedName name="_10_Instruments">'_10_Instruments'!$A$1:$J$176</definedName>
+    <definedName name="_10_Instruments">'_10_Instruments'!$A$1:$J$177</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J176"/>
+  <dimension ref="A1:J177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -3834,13 +3834,8 @@
       <c r="E110" s="0">
         <v>1</v>
       </c>
-      <c r="F110" s="0" t="inlineStr">
-        <is>
-          <t>No items</t>
-        </is>
-      </c>
       <c r="G110" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="0" t="b">
         <v>0</v>
@@ -3870,13 +3865,8 @@
       <c r="E111" s="0">
         <v>2</v>
       </c>
-      <c r="F111" s="0" t="inlineStr">
-        <is>
-          <t>No items</t>
-        </is>
-      </c>
       <c r="G111" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="0" t="b">
         <v>0</v>
@@ -4220,13 +4210,8 @@
       <c r="E121" s="0">
         <v>1</v>
       </c>
-      <c r="F121" s="0" t="inlineStr">
-        <is>
-          <t>No items</t>
-        </is>
-      </c>
       <c r="G121" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" s="0" t="b">
         <v>0</v>
@@ -4406,7 +4391,7 @@
         </is>
       </c>
       <c r="G126" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126" s="0" t="b">
         <v>0</v>
@@ -5416,16 +5401,11 @@
       <c r="E157" s="0">
         <v>2</v>
       </c>
-      <c r="F157" s="0" t="inlineStr">
-        <is>
-          <t>gender neutral version. Needs to be entered</t>
-        </is>
-      </c>
       <c r="G157" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I157" s="0" t="b">
         <v>0</v>
@@ -5452,16 +5432,11 @@
       <c r="E158" s="0">
         <v>2</v>
       </c>
-      <c r="F158" s="0" t="inlineStr">
-        <is>
-          <t>gender neutral version. Needs to be entered</t>
-        </is>
-      </c>
       <c r="G158" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I158" s="0" t="b">
         <v>0</v>
@@ -5488,16 +5463,11 @@
       <c r="E159" s="0">
         <v>1</v>
       </c>
-      <c r="F159" s="0" t="inlineStr">
-        <is>
-          <t>needs to be entered</t>
-        </is>
-      </c>
       <c r="G159" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159" s="0" t="b">
         <v>0</v>
@@ -5524,16 +5494,11 @@
       <c r="E160" s="0">
         <v>2</v>
       </c>
-      <c r="F160" s="0" t="inlineStr">
-        <is>
-          <t>needs to be entered</t>
-        </is>
-      </c>
       <c r="G160" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H160" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" s="0" t="b">
         <v>0</v>
@@ -5548,7 +5513,7 @@
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>RCADS-25-Y-NY</t>
+          <t>RCADS-25-Y-NY-1</t>
         </is>
       </c>
       <c r="C161" s="0">
@@ -5562,14 +5527,14 @@
       </c>
       <c r="F161" s="0" t="inlineStr">
         <is>
-          <t>needs to be entered</t>
+          <t>Inconsistent codebook response option</t>
         </is>
       </c>
       <c r="G161" s="0" t="b">
         <v>1</v>
       </c>
       <c r="H161" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161" s="0" t="b">
         <v>0</v>
@@ -5596,16 +5561,11 @@
       <c r="E162" s="0">
         <v>2</v>
       </c>
-      <c r="F162" s="0" t="inlineStr">
-        <is>
-          <t>needs to be entered</t>
-        </is>
-      </c>
       <c r="G162" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" s="0" t="b">
         <v>0</v>
@@ -5943,7 +5903,7 @@
         <v>1</v>
       </c>
       <c r="G173" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173" s="0" t="b">
         <v>1</v>
@@ -5974,7 +5934,7 @@
         <v>2</v>
       </c>
       <c r="G174" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H174" s="0" t="b">
         <v>1</v>
@@ -6005,7 +5965,7 @@
         <v>1</v>
       </c>
       <c r="G175" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H175" s="0" t="b">
         <v>1</v>
@@ -6036,7 +5996,7 @@
         <v>2</v>
       </c>
       <c r="G176" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" s="0" t="b">
         <v>1</v>
@@ -6045,6 +6005,37 @@
         <v>0</v>
       </c>
       <c r="J176" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="177">
+      <c r="A177" s="0">
+        <v>176</v>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-Y-NY-2</t>
+        </is>
+      </c>
+      <c r="C177" s="0">
+        <v>1</v>
+      </c>
+      <c r="D177" s="0">
+        <v>34</v>
+      </c>
+      <c r="E177" s="0">
+        <v>1</v>
+      </c>
+      <c r="G177" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H177" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I177" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J177" s="0" t="b">
         <v>0</v>
       </c>
     </row>

--- a/rcads/data/xls/10_Instruments.xlsx
+++ b/rcads/data/xls/10_Instruments.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_10_Instruments"/>
   </sheets>
   <definedNames>
-    <definedName name="_10_Instruments">'_10_Instruments'!$A$1:$K$189</definedName>
+    <definedName name="_10_Instruments">'_10_Instruments'!$A$1:$J$194</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K189"/>
+  <dimension ref="A1:K194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -369,39 +369,35 @@
       </c>
       <c r="E1" s="0" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Informant</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
         <is>
-          <t>Informant</t>
+          <t>Annotation</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
         <is>
-          <t>Annotation</t>
+          <t>Deprecated</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
         <is>
-          <t>Deprecated</t>
+          <t>Authorized</t>
         </is>
       </c>
       <c r="I1" s="0" t="inlineStr">
         <is>
-          <t>Authorized</t>
+          <t>ReadRighttoLeft</t>
         </is>
       </c>
       <c r="J1" s="0" t="inlineStr">
         <is>
-          <t>ReadRighttoLeft</t>
-        </is>
-      </c>
-      <c r="K1" s="0" t="inlineStr">
-        <is>
           <t>Unavailable(NotGenerated)</t>
         </is>
       </c>
+      <c r="K1" s="0" t="inlineStr"/>
     </row>
     <row outlineLevel="0" r="2">
       <c r="A2" s="0">
@@ -421,21 +417,20 @@
       <c r="E2" s="0">
         <v>1</v>
       </c>
-      <c r="F2" s="0">
-        <v>1</v>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H2" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K2" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K2" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="3">
       <c r="A3" s="0">
@@ -453,23 +448,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="0">
-        <v>1</v>
-      </c>
-      <c r="F3" s="0">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H3" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K3" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K3" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="4">
       <c r="A4" s="0">
@@ -489,21 +483,20 @@
       <c r="E4" s="0">
         <v>1</v>
       </c>
-      <c r="F4" s="0">
-        <v>1</v>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H4" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K4" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K4" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="5">
       <c r="A5" s="0">
@@ -521,23 +514,22 @@
         <v>1</v>
       </c>
       <c r="E5" s="0">
-        <v>1</v>
-      </c>
-      <c r="F5" s="0">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H5" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K5" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K5" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="6">
       <c r="A6" s="0">
@@ -555,23 +547,22 @@
         <v>9</v>
       </c>
       <c r="E6" s="0">
-        <v>5</v>
-      </c>
-      <c r="F6" s="0">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H6" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K6" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K6" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="7">
       <c r="A7" s="0">
@@ -589,23 +580,22 @@
         <v>9</v>
       </c>
       <c r="E7" s="0">
-        <v>5</v>
-      </c>
-      <c r="F7" s="0">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H7" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K7" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K7" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="8">
       <c r="A8" s="0">
@@ -623,23 +613,22 @@
         <v>9</v>
       </c>
       <c r="E8" s="0">
-        <v>5</v>
-      </c>
-      <c r="F8" s="0">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F8" s="0"/>
+      <c r="G8" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H8" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K8" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="9">
       <c r="A9" s="0">
@@ -657,23 +646,22 @@
         <v>9</v>
       </c>
       <c r="E9" s="0">
-        <v>5</v>
-      </c>
-      <c r="F9" s="0">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H9" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K9" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K9" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="10">
       <c r="A10" s="0">
@@ -691,23 +679,22 @@
         <v>4</v>
       </c>
       <c r="E10" s="0">
-        <v>2</v>
-      </c>
-      <c r="F10" s="0">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H10" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K10" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K10" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="11">
       <c r="A11" s="0">
@@ -727,21 +714,20 @@
       <c r="E11" s="0">
         <v>2</v>
       </c>
-      <c r="F11" s="0">
-        <v>2</v>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H11" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K11" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K11" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="12">
       <c r="A12" s="0">
@@ -759,23 +745,22 @@
         <v>4</v>
       </c>
       <c r="E12" s="0">
-        <v>2</v>
-      </c>
-      <c r="F12" s="0">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H12" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K12" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K12" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="13">
       <c r="A13" s="0">
@@ -795,21 +780,20 @@
       <c r="E13" s="0">
         <v>2</v>
       </c>
-      <c r="F13" s="0">
-        <v>2</v>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H13" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K13" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K13" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="14">
       <c r="A14" s="0">
@@ -827,16 +811,18 @@
         <v>8</v>
       </c>
       <c r="E14" s="0">
-        <v>4</v>
-      </c>
-      <c r="F14" s="0">
-        <v>1</v>
-      </c>
-      <c r="G14" s="0" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>OG Bouvard version - has empirical study validating this version</t>
         </is>
       </c>
+      <c r="G14" s="0" t="b">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H14" s="0" t="b">
         <v>0</v>
       </c>
@@ -846,9 +832,7 @@
       <c r="J14" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K14" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K14" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="15">
       <c r="A15" s="0">
@@ -866,18 +850,20 @@
         <v>8</v>
       </c>
       <c r="E15" s="0">
-        <v>8</v>
-      </c>
-      <c r="F15" s="0">
-        <v>2</v>
-      </c>
-      <c r="G15" s="0" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>Chantal Caron et al 2018</t>
         </is>
       </c>
+      <c r="G15" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H15" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="0" t="b">
         <v>0</v>
@@ -885,9 +871,7 @@
       <c r="J15" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K15" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K15" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="16">
       <c r="A16" s="0">
@@ -905,16 +889,18 @@
         <v>8</v>
       </c>
       <c r="E16" s="0">
-        <v>4</v>
-      </c>
-      <c r="F16" s="0">
-        <v>1</v>
-      </c>
-      <c r="G16" s="0" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>RCADS team generated</t>
         </is>
       </c>
+      <c r="G16" s="0" t="b">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H16" s="0" t="b">
         <v>0</v>
       </c>
@@ -924,9 +910,7 @@
       <c r="J16" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K16" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K16" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="17">
       <c r="A17" s="0">
@@ -944,28 +928,28 @@
         <v>8</v>
       </c>
       <c r="E17" s="0">
-        <v>4</v>
-      </c>
-      <c r="F17" s="0">
-        <v>2</v>
-      </c>
-      <c r="G17" s="0" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>No items; Based on Boustani update of France French version</t>
         </is>
       </c>
+      <c r="G17" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H17" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J17" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K17" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="18">
       <c r="A18" s="0">
@@ -982,8 +966,12 @@
       <c r="D18" s="0">
         <v>21</v>
       </c>
-      <c r="F18" s="0">
-        <v>1</v>
+      <c r="E18" s="0">
+        <v>1</v>
+      </c>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H18" s="0" t="b">
         <v>0</v>
@@ -994,9 +982,7 @@
       <c r="J18" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K18" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K18" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="19">
       <c r="A19" s="0">
@@ -1013,8 +999,12 @@
       <c r="D19" s="0">
         <v>21</v>
       </c>
-      <c r="F19" s="0">
-        <v>2</v>
+      <c r="E19" s="0">
+        <v>2</v>
+      </c>
+      <c r="F19" s="0"/>
+      <c r="G19" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H19" s="0" t="b">
         <v>0</v>
@@ -1025,9 +1015,7 @@
       <c r="J19" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K19" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K19" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="20">
       <c r="A20" s="0">
@@ -1044,8 +1032,12 @@
       <c r="D20" s="0">
         <v>21</v>
       </c>
-      <c r="F20" s="0">
-        <v>1</v>
+      <c r="E20" s="0">
+        <v>1</v>
+      </c>
+      <c r="F20" s="0"/>
+      <c r="G20" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H20" s="0" t="b">
         <v>0</v>
@@ -1056,9 +1048,7 @@
       <c r="J20" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K20" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K20" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="21">
       <c r="A21" s="0">
@@ -1075,8 +1065,12 @@
       <c r="D21" s="0">
         <v>21</v>
       </c>
-      <c r="F21" s="0">
-        <v>2</v>
+      <c r="E21" s="0">
+        <v>2</v>
+      </c>
+      <c r="F21" s="0"/>
+      <c r="G21" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H21" s="0" t="b">
         <v>0</v>
@@ -1087,9 +1081,7 @@
       <c r="J21" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K21" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K21" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="22">
       <c r="A22" s="0">
@@ -1106,21 +1098,23 @@
       <c r="D22" s="0">
         <v>2</v>
       </c>
-      <c r="F22" s="0">
-        <v>1</v>
+      <c r="E22" s="0">
+        <v>1</v>
+      </c>
+      <c r="F22" s="0"/>
+      <c r="G22" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H22" s="0" t="b">
         <v>0</v>
       </c>
       <c r="I22" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="0" t="b">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K22" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="23">
       <c r="A23" s="0">
@@ -1137,21 +1131,23 @@
       <c r="D23" s="0">
         <v>2</v>
       </c>
-      <c r="F23" s="0">
-        <v>2</v>
+      <c r="E23" s="0">
+        <v>2</v>
+      </c>
+      <c r="F23" s="0"/>
+      <c r="G23" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H23" s="0" t="b">
         <v>0</v>
       </c>
       <c r="I23" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" s="0" t="b">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K23" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="24">
       <c r="A24" s="0">
@@ -1168,21 +1164,23 @@
       <c r="D24" s="0">
         <v>2</v>
       </c>
-      <c r="F24" s="0">
-        <v>1</v>
+      <c r="E24" s="0">
+        <v>1</v>
+      </c>
+      <c r="F24" s="0"/>
+      <c r="G24" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H24" s="0" t="b">
         <v>0</v>
       </c>
       <c r="I24" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" s="0" t="b">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K24" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="25">
       <c r="A25" s="0">
@@ -1199,21 +1197,23 @@
       <c r="D25" s="0">
         <v>2</v>
       </c>
-      <c r="F25" s="0">
-        <v>2</v>
+      <c r="E25" s="0">
+        <v>2</v>
+      </c>
+      <c r="F25" s="0"/>
+      <c r="G25" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H25" s="0" t="b">
         <v>0</v>
       </c>
       <c r="I25" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" s="0" t="b">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K25" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="26">
       <c r="A26" s="0">
@@ -1230,8 +1230,12 @@
       <c r="D26" s="0">
         <v>3</v>
       </c>
-      <c r="F26" s="0">
-        <v>1</v>
+      <c r="E26" s="0">
+        <v>1</v>
+      </c>
+      <c r="F26" s="0"/>
+      <c r="G26" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H26" s="0" t="b">
         <v>0</v>
@@ -1242,9 +1246,7 @@
       <c r="J26" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K26" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K26" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="27">
       <c r="A27" s="0">
@@ -1261,8 +1263,12 @@
       <c r="D27" s="0">
         <v>3</v>
       </c>
-      <c r="F27" s="0">
-        <v>2</v>
+      <c r="E27" s="0">
+        <v>2</v>
+      </c>
+      <c r="F27" s="0"/>
+      <c r="G27" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H27" s="0" t="b">
         <v>0</v>
@@ -1273,9 +1279,7 @@
       <c r="J27" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K27" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K27" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="28">
       <c r="A28" s="0">
@@ -1292,8 +1296,12 @@
       <c r="D28" s="0">
         <v>3</v>
       </c>
-      <c r="F28" s="0">
-        <v>1</v>
+      <c r="E28" s="0">
+        <v>1</v>
+      </c>
+      <c r="F28" s="0"/>
+      <c r="G28" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H28" s="0" t="b">
         <v>0</v>
@@ -1304,9 +1312,7 @@
       <c r="J28" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K28" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K28" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="29">
       <c r="A29" s="0">
@@ -1323,8 +1329,12 @@
       <c r="D29" s="0">
         <v>3</v>
       </c>
-      <c r="F29" s="0">
-        <v>2</v>
+      <c r="E29" s="0">
+        <v>2</v>
+      </c>
+      <c r="F29" s="0"/>
+      <c r="G29" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H29" s="0" t="b">
         <v>0</v>
@@ -1335,9 +1345,7 @@
       <c r="J29" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K29" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K29" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="30">
       <c r="A30" s="0">
@@ -1355,10 +1363,11 @@
         <v>5</v>
       </c>
       <c r="E30" s="0">
-        <v>3</v>
-      </c>
-      <c r="F30" s="0">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F30" s="0"/>
+      <c r="G30" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H30" s="0" t="b">
         <v>0</v>
@@ -1369,9 +1378,7 @@
       <c r="J30" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K30" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K30" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="31">
       <c r="A31" s="0">
@@ -1389,10 +1396,11 @@
         <v>5</v>
       </c>
       <c r="E31" s="0">
-        <v>3</v>
-      </c>
-      <c r="F31" s="0">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="F31" s="0"/>
+      <c r="G31" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H31" s="0" t="b">
         <v>0</v>
@@ -1403,9 +1411,7 @@
       <c r="J31" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K31" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K31" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="0">
@@ -1423,10 +1429,11 @@
         <v>5</v>
       </c>
       <c r="E32" s="0">
-        <v>3</v>
-      </c>
-      <c r="F32" s="0">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F32" s="0"/>
+      <c r="G32" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H32" s="0" t="b">
         <v>0</v>
@@ -1437,9 +1444,7 @@
       <c r="J32" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K32" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K32" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="33">
       <c r="A33" s="0">
@@ -1457,10 +1462,11 @@
         <v>5</v>
       </c>
       <c r="E33" s="0">
-        <v>3</v>
-      </c>
-      <c r="F33" s="0">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="F33" s="0"/>
+      <c r="G33" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H33" s="0" t="b">
         <v>0</v>
@@ -1471,9 +1477,7 @@
       <c r="J33" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K33" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K33" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="34">
       <c r="A34" s="0">
@@ -1490,8 +1494,12 @@
       <c r="D34" s="0">
         <v>6</v>
       </c>
-      <c r="F34" s="0">
-        <v>1</v>
+      <c r="E34" s="0">
+        <v>1</v>
+      </c>
+      <c r="F34" s="0"/>
+      <c r="G34" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H34" s="0" t="b">
         <v>0</v>
@@ -1502,9 +1510,7 @@
       <c r="J34" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K34" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K34" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="35">
       <c r="A35" s="0">
@@ -1521,8 +1527,12 @@
       <c r="D35" s="0">
         <v>6</v>
       </c>
-      <c r="F35" s="0">
-        <v>2</v>
+      <c r="E35" s="0">
+        <v>2</v>
+      </c>
+      <c r="F35" s="0"/>
+      <c r="G35" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H35" s="0" t="b">
         <v>0</v>
@@ -1533,9 +1543,7 @@
       <c r="J35" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K35" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K35" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="36">
       <c r="A36" s="0">
@@ -1552,8 +1560,12 @@
       <c r="D36" s="0">
         <v>6</v>
       </c>
-      <c r="F36" s="0">
-        <v>1</v>
+      <c r="E36" s="0">
+        <v>1</v>
+      </c>
+      <c r="F36" s="0"/>
+      <c r="G36" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H36" s="0" t="b">
         <v>0</v>
@@ -1564,9 +1576,7 @@
       <c r="J36" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K36" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K36" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="37">
       <c r="A37" s="0">
@@ -1583,8 +1593,12 @@
       <c r="D37" s="0">
         <v>6</v>
       </c>
-      <c r="F37" s="0">
-        <v>2</v>
+      <c r="E37" s="0">
+        <v>2</v>
+      </c>
+      <c r="F37" s="0"/>
+      <c r="G37" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H37" s="0" t="b">
         <v>0</v>
@@ -1595,9 +1609,7 @@
       <c r="J37" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K37" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K37" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="38">
       <c r="A38" s="0">
@@ -1614,8 +1626,12 @@
       <c r="D38" s="0">
         <v>7</v>
       </c>
-      <c r="F38" s="0">
-        <v>1</v>
+      <c r="E38" s="0">
+        <v>1</v>
+      </c>
+      <c r="F38" s="0"/>
+      <c r="G38" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H38" s="0" t="b">
         <v>0</v>
@@ -1626,9 +1642,7 @@
       <c r="J38" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K38" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K38" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="39">
       <c r="A39" s="0">
@@ -1645,8 +1659,12 @@
       <c r="D39" s="0">
         <v>7</v>
       </c>
-      <c r="F39" s="0">
-        <v>2</v>
+      <c r="E39" s="0">
+        <v>2</v>
+      </c>
+      <c r="F39" s="0"/>
+      <c r="G39" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H39" s="0" t="b">
         <v>0</v>
@@ -1657,9 +1675,7 @@
       <c r="J39" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K39" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K39" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="40">
       <c r="A40" s="0">
@@ -1676,8 +1692,12 @@
       <c r="D40" s="0">
         <v>7</v>
       </c>
-      <c r="F40" s="0">
-        <v>1</v>
+      <c r="E40" s="0">
+        <v>1</v>
+      </c>
+      <c r="F40" s="0"/>
+      <c r="G40" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H40" s="0" t="b">
         <v>0</v>
@@ -1688,9 +1708,7 @@
       <c r="J40" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K40" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K40" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="41">
       <c r="A41" s="0">
@@ -1707,8 +1725,12 @@
       <c r="D41" s="0">
         <v>7</v>
       </c>
-      <c r="F41" s="0">
-        <v>2</v>
+      <c r="E41" s="0">
+        <v>2</v>
+      </c>
+      <c r="F41" s="0"/>
+      <c r="G41" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H41" s="0" t="b">
         <v>0</v>
@@ -1719,9 +1741,7 @@
       <c r="J41" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K41" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K41" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="42">
       <c r="A42" s="0">
@@ -1738,8 +1758,12 @@
       <c r="D42" s="0">
         <v>10</v>
       </c>
-      <c r="F42" s="0">
-        <v>1</v>
+      <c r="E42" s="0">
+        <v>1</v>
+      </c>
+      <c r="F42" s="0"/>
+      <c r="G42" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H42" s="0" t="b">
         <v>0</v>
@@ -1750,9 +1774,7 @@
       <c r="J42" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K42" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K42" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="43">
       <c r="A43" s="0">
@@ -1769,8 +1791,12 @@
       <c r="D43" s="0">
         <v>10</v>
       </c>
-      <c r="F43" s="0">
-        <v>2</v>
+      <c r="E43" s="0">
+        <v>2</v>
+      </c>
+      <c r="F43" s="0"/>
+      <c r="G43" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H43" s="0" t="b">
         <v>0</v>
@@ -1781,9 +1807,7 @@
       <c r="J43" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K43" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K43" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="44">
       <c r="A44" s="0">
@@ -1800,8 +1824,12 @@
       <c r="D44" s="0">
         <v>10</v>
       </c>
-      <c r="F44" s="0">
-        <v>1</v>
+      <c r="E44" s="0">
+        <v>1</v>
+      </c>
+      <c r="F44" s="0"/>
+      <c r="G44" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H44" s="0" t="b">
         <v>0</v>
@@ -1812,9 +1840,7 @@
       <c r="J44" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K44" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K44" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="45">
       <c r="A45" s="0">
@@ -1831,8 +1857,12 @@
       <c r="D45" s="0">
         <v>10</v>
       </c>
-      <c r="F45" s="0">
-        <v>2</v>
+      <c r="E45" s="0">
+        <v>2</v>
+      </c>
+      <c r="F45" s="0"/>
+      <c r="G45" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H45" s="0" t="b">
         <v>0</v>
@@ -1843,9 +1873,7 @@
       <c r="J45" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K45" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K45" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="46">
       <c r="A46" s="0">
@@ -1862,8 +1890,12 @@
       <c r="D46" s="0">
         <v>11</v>
       </c>
-      <c r="F46" s="0">
-        <v>1</v>
+      <c r="E46" s="0">
+        <v>1</v>
+      </c>
+      <c r="F46" s="0"/>
+      <c r="G46" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H46" s="0" t="b">
         <v>0</v>
@@ -1874,9 +1906,7 @@
       <c r="J46" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K46" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K46" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="47">
       <c r="A47" s="0">
@@ -1893,8 +1923,12 @@
       <c r="D47" s="0">
         <v>11</v>
       </c>
-      <c r="F47" s="0">
-        <v>2</v>
+      <c r="E47" s="0">
+        <v>2</v>
+      </c>
+      <c r="F47" s="0"/>
+      <c r="G47" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H47" s="0" t="b">
         <v>0</v>
@@ -1905,9 +1939,7 @@
       <c r="J47" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K47" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K47" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="48">
       <c r="A48" s="0">
@@ -1924,8 +1956,12 @@
       <c r="D48" s="0">
         <v>11</v>
       </c>
-      <c r="F48" s="0">
-        <v>1</v>
+      <c r="E48" s="0">
+        <v>1</v>
+      </c>
+      <c r="F48" s="0"/>
+      <c r="G48" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H48" s="0" t="b">
         <v>0</v>
@@ -1936,9 +1972,7 @@
       <c r="J48" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K48" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K48" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="49">
       <c r="A49" s="0">
@@ -1955,8 +1989,12 @@
       <c r="D49" s="0">
         <v>11</v>
       </c>
-      <c r="F49" s="0">
-        <v>2</v>
+      <c r="E49" s="0">
+        <v>2</v>
+      </c>
+      <c r="F49" s="0"/>
+      <c r="G49" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H49" s="0" t="b">
         <v>0</v>
@@ -1967,9 +2005,7 @@
       <c r="J49" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K49" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K49" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="50">
       <c r="A50" s="0">
@@ -1986,8 +2022,12 @@
       <c r="D50" s="0">
         <v>12</v>
       </c>
-      <c r="F50" s="0">
-        <v>1</v>
+      <c r="E50" s="0">
+        <v>1</v>
+      </c>
+      <c r="F50" s="0"/>
+      <c r="G50" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H50" s="0" t="b">
         <v>0</v>
@@ -1998,9 +2038,7 @@
       <c r="J50" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K50" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K50" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="51">
       <c r="A51" s="0">
@@ -2017,8 +2055,12 @@
       <c r="D51" s="0">
         <v>12</v>
       </c>
-      <c r="F51" s="0">
-        <v>2</v>
+      <c r="E51" s="0">
+        <v>2</v>
+      </c>
+      <c r="F51" s="0"/>
+      <c r="G51" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H51" s="0" t="b">
         <v>0</v>
@@ -2029,9 +2071,7 @@
       <c r="J51" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K51" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K51" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="52">
       <c r="A52" s="0">
@@ -2048,8 +2088,12 @@
       <c r="D52" s="0">
         <v>12</v>
       </c>
-      <c r="F52" s="0">
-        <v>1</v>
+      <c r="E52" s="0">
+        <v>1</v>
+      </c>
+      <c r="F52" s="0"/>
+      <c r="G52" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H52" s="0" t="b">
         <v>0</v>
@@ -2060,9 +2104,7 @@
       <c r="J52" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K52" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K52" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="53">
       <c r="A53" s="0">
@@ -2079,8 +2121,12 @@
       <c r="D53" s="0">
         <v>12</v>
       </c>
-      <c r="F53" s="0">
-        <v>2</v>
+      <c r="E53" s="0">
+        <v>2</v>
+      </c>
+      <c r="F53" s="0"/>
+      <c r="G53" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H53" s="0" t="b">
         <v>0</v>
@@ -2091,9 +2137,7 @@
       <c r="J53" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K53" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K53" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="54">
       <c r="A54" s="0">
@@ -2110,8 +2154,12 @@
       <c r="D54" s="0">
         <v>13</v>
       </c>
-      <c r="F54" s="0">
-        <v>1</v>
+      <c r="E54" s="0">
+        <v>1</v>
+      </c>
+      <c r="F54" s="0"/>
+      <c r="G54" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H54" s="0" t="b">
         <v>0</v>
@@ -2122,9 +2170,7 @@
       <c r="J54" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K54" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K54" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="55">
       <c r="A55" s="0">
@@ -2141,8 +2187,12 @@
       <c r="D55" s="0">
         <v>13</v>
       </c>
-      <c r="F55" s="0">
-        <v>2</v>
+      <c r="E55" s="0">
+        <v>2</v>
+      </c>
+      <c r="F55" s="0"/>
+      <c r="G55" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H55" s="0" t="b">
         <v>0</v>
@@ -2153,9 +2203,7 @@
       <c r="J55" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K55" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K55" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="0">
@@ -2172,8 +2220,12 @@
       <c r="D56" s="0">
         <v>13</v>
       </c>
-      <c r="F56" s="0">
-        <v>1</v>
+      <c r="E56" s="0">
+        <v>1</v>
+      </c>
+      <c r="F56" s="0"/>
+      <c r="G56" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H56" s="0" t="b">
         <v>0</v>
@@ -2184,9 +2236,7 @@
       <c r="J56" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K56" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K56" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="57">
       <c r="A57" s="0">
@@ -2203,8 +2253,12 @@
       <c r="D57" s="0">
         <v>13</v>
       </c>
-      <c r="F57" s="0">
-        <v>2</v>
+      <c r="E57" s="0">
+        <v>2</v>
+      </c>
+      <c r="F57" s="0"/>
+      <c r="G57" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H57" s="0" t="b">
         <v>0</v>
@@ -2215,9 +2269,7 @@
       <c r="J57" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K57" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K57" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="58">
       <c r="A58" s="0">
@@ -2234,8 +2286,12 @@
       <c r="D58" s="0">
         <v>14</v>
       </c>
-      <c r="F58" s="0">
-        <v>1</v>
+      <c r="E58" s="0">
+        <v>1</v>
+      </c>
+      <c r="F58" s="0"/>
+      <c r="G58" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H58" s="0" t="b">
         <v>0</v>
@@ -2246,9 +2302,7 @@
       <c r="J58" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K58" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K58" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="0">
@@ -2265,8 +2319,12 @@
       <c r="D59" s="0">
         <v>14</v>
       </c>
-      <c r="F59" s="0">
-        <v>2</v>
+      <c r="E59" s="0">
+        <v>2</v>
+      </c>
+      <c r="F59" s="0"/>
+      <c r="G59" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H59" s="0" t="b">
         <v>0</v>
@@ -2277,9 +2335,7 @@
       <c r="J59" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K59" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K59" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="0">
@@ -2296,8 +2352,12 @@
       <c r="D60" s="0">
         <v>14</v>
       </c>
-      <c r="F60" s="0">
-        <v>1</v>
+      <c r="E60" s="0">
+        <v>1</v>
+      </c>
+      <c r="F60" s="0"/>
+      <c r="G60" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H60" s="0" t="b">
         <v>0</v>
@@ -2308,9 +2368,7 @@
       <c r="J60" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K60" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K60" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="61">
       <c r="A61" s="0">
@@ -2327,8 +2385,12 @@
       <c r="D61" s="0">
         <v>14</v>
       </c>
-      <c r="F61" s="0">
-        <v>2</v>
+      <c r="E61" s="0">
+        <v>2</v>
+      </c>
+      <c r="F61" s="0"/>
+      <c r="G61" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H61" s="0" t="b">
         <v>0</v>
@@ -2339,9 +2401,7 @@
       <c r="J61" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K61" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K61" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="0">
@@ -2358,8 +2418,12 @@
       <c r="D62" s="0">
         <v>15</v>
       </c>
-      <c r="F62" s="0">
-        <v>1</v>
+      <c r="E62" s="0">
+        <v>1</v>
+      </c>
+      <c r="F62" s="0"/>
+      <c r="G62" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H62" s="0" t="b">
         <v>0</v>
@@ -2370,9 +2434,7 @@
       <c r="J62" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K62" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K62" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="0">
@@ -2389,26 +2451,29 @@
       <c r="D63" s="0">
         <v>15</v>
       </c>
-      <c r="F63" s="0">
-        <v>2</v>
-      </c>
-      <c r="G63" s="0" t="inlineStr">
+      <c r="E63" s="0">
+        <v>2</v>
+      </c>
+      <c r="F63" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G63" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H63" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J63" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K63" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="0">
@@ -2425,8 +2490,12 @@
       <c r="D64" s="0">
         <v>15</v>
       </c>
-      <c r="F64" s="0">
-        <v>1</v>
+      <c r="E64" s="0">
+        <v>1</v>
+      </c>
+      <c r="F64" s="0"/>
+      <c r="G64" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H64" s="0" t="b">
         <v>0</v>
@@ -2437,9 +2506,7 @@
       <c r="J64" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K64" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K64" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="65">
       <c r="A65" s="0">
@@ -2456,26 +2523,29 @@
       <c r="D65" s="0">
         <v>15</v>
       </c>
-      <c r="F65" s="0">
-        <v>2</v>
-      </c>
-      <c r="G65" s="0" t="inlineStr">
+      <c r="E65" s="0">
+        <v>2</v>
+      </c>
+      <c r="F65" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G65" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H65" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J65" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K65" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="0">
@@ -2492,8 +2562,12 @@
       <c r="D66" s="0">
         <v>16</v>
       </c>
-      <c r="F66" s="0">
-        <v>1</v>
+      <c r="E66" s="0">
+        <v>1</v>
+      </c>
+      <c r="F66" s="0"/>
+      <c r="G66" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H66" s="0" t="b">
         <v>0</v>
@@ -2504,9 +2578,7 @@
       <c r="J66" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K66" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K66" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="0">
@@ -2523,8 +2595,12 @@
       <c r="D67" s="0">
         <v>16</v>
       </c>
-      <c r="F67" s="0">
-        <v>2</v>
+      <c r="E67" s="0">
+        <v>2</v>
+      </c>
+      <c r="F67" s="0"/>
+      <c r="G67" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H67" s="0" t="b">
         <v>0</v>
@@ -2535,9 +2611,7 @@
       <c r="J67" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K67" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K67" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="0">
@@ -2554,8 +2628,12 @@
       <c r="D68" s="0">
         <v>16</v>
       </c>
-      <c r="F68" s="0">
-        <v>1</v>
+      <c r="E68" s="0">
+        <v>1</v>
+      </c>
+      <c r="F68" s="0"/>
+      <c r="G68" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H68" s="0" t="b">
         <v>0</v>
@@ -2566,9 +2644,7 @@
       <c r="J68" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K68" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K68" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="69">
       <c r="A69" s="0">
@@ -2585,8 +2661,12 @@
       <c r="D69" s="0">
         <v>16</v>
       </c>
-      <c r="F69" s="0">
-        <v>2</v>
+      <c r="E69" s="0">
+        <v>2</v>
+      </c>
+      <c r="F69" s="0"/>
+      <c r="G69" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H69" s="0" t="b">
         <v>0</v>
@@ -2597,9 +2677,7 @@
       <c r="J69" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K69" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K69" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="70">
       <c r="A70" s="0">
@@ -2616,8 +2694,12 @@
       <c r="D70" s="0">
         <v>17</v>
       </c>
-      <c r="F70" s="0">
-        <v>1</v>
+      <c r="E70" s="0">
+        <v>1</v>
+      </c>
+      <c r="F70" s="0"/>
+      <c r="G70" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H70" s="0" t="b">
         <v>0</v>
@@ -2628,9 +2710,7 @@
       <c r="J70" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K70" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K70" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="71">
       <c r="A71" s="0">
@@ -2647,8 +2727,12 @@
       <c r="D71" s="0">
         <v>17</v>
       </c>
-      <c r="F71" s="0">
-        <v>2</v>
+      <c r="E71" s="0">
+        <v>2</v>
+      </c>
+      <c r="F71" s="0"/>
+      <c r="G71" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H71" s="0" t="b">
         <v>0</v>
@@ -2659,9 +2743,7 @@
       <c r="J71" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K71" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K71" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="72">
       <c r="A72" s="0">
@@ -2678,8 +2760,12 @@
       <c r="D72" s="0">
         <v>17</v>
       </c>
-      <c r="F72" s="0">
-        <v>1</v>
+      <c r="E72" s="0">
+        <v>1</v>
+      </c>
+      <c r="F72" s="0"/>
+      <c r="G72" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H72" s="0" t="b">
         <v>0</v>
@@ -2690,9 +2776,7 @@
       <c r="J72" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K72" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K72" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="73">
       <c r="A73" s="0">
@@ -2709,8 +2793,12 @@
       <c r="D73" s="0">
         <v>17</v>
       </c>
-      <c r="F73" s="0">
-        <v>2</v>
+      <c r="E73" s="0">
+        <v>2</v>
+      </c>
+      <c r="F73" s="0"/>
+      <c r="G73" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H73" s="0" t="b">
         <v>0</v>
@@ -2721,9 +2809,7 @@
       <c r="J73" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K73" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K73" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="74">
       <c r="A74" s="0">
@@ -2740,8 +2826,12 @@
       <c r="D74" s="0">
         <v>18</v>
       </c>
-      <c r="F74" s="0">
-        <v>1</v>
+      <c r="E74" s="0">
+        <v>1</v>
+      </c>
+      <c r="F74" s="0"/>
+      <c r="G74" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H74" s="0" t="b">
         <v>0</v>
@@ -2752,9 +2842,7 @@
       <c r="J74" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K74" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K74" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="0">
@@ -2771,8 +2859,12 @@
       <c r="D75" s="0">
         <v>18</v>
       </c>
-      <c r="F75" s="0">
-        <v>2</v>
+      <c r="E75" s="0">
+        <v>2</v>
+      </c>
+      <c r="F75" s="0"/>
+      <c r="G75" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H75" s="0" t="b">
         <v>0</v>
@@ -2783,9 +2875,7 @@
       <c r="J75" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K75" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K75" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="0">
@@ -2802,8 +2892,12 @@
       <c r="D76" s="0">
         <v>18</v>
       </c>
-      <c r="F76" s="0">
-        <v>1</v>
+      <c r="E76" s="0">
+        <v>1</v>
+      </c>
+      <c r="F76" s="0"/>
+      <c r="G76" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H76" s="0" t="b">
         <v>0</v>
@@ -2814,9 +2908,7 @@
       <c r="J76" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K76" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K76" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="0">
@@ -2833,8 +2925,12 @@
       <c r="D77" s="0">
         <v>18</v>
       </c>
-      <c r="F77" s="0">
-        <v>2</v>
+      <c r="E77" s="0">
+        <v>2</v>
+      </c>
+      <c r="F77" s="0"/>
+      <c r="G77" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H77" s="0" t="b">
         <v>0</v>
@@ -2845,9 +2941,7 @@
       <c r="J77" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K77" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K77" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="0">
@@ -2865,10 +2959,11 @@
         <v>19</v>
       </c>
       <c r="E78" s="0">
-        <v>7</v>
-      </c>
-      <c r="F78" s="0">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F78" s="0"/>
+      <c r="G78" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H78" s="0" t="b">
         <v>0</v>
@@ -2879,9 +2974,7 @@
       <c r="J78" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K78" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K78" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="79">
       <c r="A79" s="0">
@@ -2898,26 +2991,29 @@
       <c r="D79" s="0">
         <v>19</v>
       </c>
-      <c r="F79" s="0">
-        <v>2</v>
-      </c>
-      <c r="G79" s="0" t="inlineStr">
+      <c r="E79" s="0">
+        <v>2</v>
+      </c>
+      <c r="F79" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G79" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H79" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J79" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K79" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="0">
@@ -2935,10 +3031,11 @@
         <v>19</v>
       </c>
       <c r="E80" s="0">
-        <v>7</v>
-      </c>
-      <c r="F80" s="0">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F80" s="0"/>
+      <c r="G80" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H80" s="0" t="b">
         <v>0</v>
@@ -2949,9 +3046,7 @@
       <c r="J80" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K80" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K80" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="81">
       <c r="A81" s="0">
@@ -2968,26 +3063,29 @@
       <c r="D81" s="0">
         <v>19</v>
       </c>
-      <c r="F81" s="0">
-        <v>2</v>
-      </c>
-      <c r="G81" s="0" t="inlineStr">
+      <c r="E81" s="0">
+        <v>2</v>
+      </c>
+      <c r="F81" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G81" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H81" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J81" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K81" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="82">
       <c r="A82" s="0">
@@ -3004,8 +3102,12 @@
       <c r="D82" s="0">
         <v>20</v>
       </c>
-      <c r="F82" s="0">
-        <v>1</v>
+      <c r="E82" s="0">
+        <v>1</v>
+      </c>
+      <c r="F82" s="0"/>
+      <c r="G82" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H82" s="0" t="b">
         <v>0</v>
@@ -3016,9 +3118,7 @@
       <c r="J82" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K82" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K82" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="83">
       <c r="A83" s="0">
@@ -3035,8 +3135,12 @@
       <c r="D83" s="0">
         <v>20</v>
       </c>
-      <c r="F83" s="0">
-        <v>2</v>
+      <c r="E83" s="0">
+        <v>2</v>
+      </c>
+      <c r="F83" s="0"/>
+      <c r="G83" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H83" s="0" t="b">
         <v>0</v>
@@ -3047,9 +3151,7 @@
       <c r="J83" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K83" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K83" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="84">
       <c r="A84" s="0">
@@ -3066,8 +3168,12 @@
       <c r="D84" s="0">
         <v>20</v>
       </c>
-      <c r="F84" s="0">
-        <v>1</v>
+      <c r="E84" s="0">
+        <v>1</v>
+      </c>
+      <c r="F84" s="0"/>
+      <c r="G84" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H84" s="0" t="b">
         <v>0</v>
@@ -3078,9 +3184,7 @@
       <c r="J84" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K84" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K84" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="0">
@@ -3097,8 +3201,12 @@
       <c r="D85" s="0">
         <v>20</v>
       </c>
-      <c r="F85" s="0">
-        <v>2</v>
+      <c r="E85" s="0">
+        <v>2</v>
+      </c>
+      <c r="F85" s="0"/>
+      <c r="G85" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H85" s="0" t="b">
         <v>0</v>
@@ -3109,9 +3217,7 @@
       <c r="J85" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K85" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K85" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="86">
       <c r="A86" s="0">
@@ -3128,8 +3234,12 @@
       <c r="D86" s="0">
         <v>22</v>
       </c>
-      <c r="F86" s="0">
-        <v>1</v>
+      <c r="E86" s="0">
+        <v>1</v>
+      </c>
+      <c r="F86" s="0"/>
+      <c r="G86" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H86" s="0" t="b">
         <v>0</v>
@@ -3140,9 +3250,7 @@
       <c r="J86" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K86" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K86" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="0">
@@ -3159,8 +3267,12 @@
       <c r="D87" s="0">
         <v>22</v>
       </c>
-      <c r="F87" s="0">
-        <v>2</v>
+      <c r="E87" s="0">
+        <v>2</v>
+      </c>
+      <c r="F87" s="0"/>
+      <c r="G87" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H87" s="0" t="b">
         <v>0</v>
@@ -3171,9 +3283,7 @@
       <c r="J87" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K87" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K87" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="0">
@@ -3190,8 +3300,12 @@
       <c r="D88" s="0">
         <v>22</v>
       </c>
-      <c r="F88" s="0">
-        <v>1</v>
+      <c r="E88" s="0">
+        <v>1</v>
+      </c>
+      <c r="F88" s="0"/>
+      <c r="G88" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H88" s="0" t="b">
         <v>0</v>
@@ -3202,9 +3316,7 @@
       <c r="J88" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K88" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K88" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="0">
@@ -3221,8 +3333,12 @@
       <c r="D89" s="0">
         <v>22</v>
       </c>
-      <c r="F89" s="0">
-        <v>2</v>
+      <c r="E89" s="0">
+        <v>2</v>
+      </c>
+      <c r="F89" s="0"/>
+      <c r="G89" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H89" s="0" t="b">
         <v>0</v>
@@ -3233,9 +3349,7 @@
       <c r="J89" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K89" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K89" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="0">
@@ -3252,8 +3366,12 @@
       <c r="D90" s="0">
         <v>23</v>
       </c>
-      <c r="F90" s="0">
-        <v>1</v>
+      <c r="E90" s="0">
+        <v>1</v>
+      </c>
+      <c r="F90" s="0"/>
+      <c r="G90" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H90" s="0" t="b">
         <v>0</v>
@@ -3264,9 +3382,7 @@
       <c r="J90" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K90" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K90" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="91">
       <c r="A91" s="0">
@@ -3283,8 +3399,12 @@
       <c r="D91" s="0">
         <v>23</v>
       </c>
-      <c r="F91" s="0">
-        <v>2</v>
+      <c r="E91" s="0">
+        <v>2</v>
+      </c>
+      <c r="F91" s="0"/>
+      <c r="G91" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H91" s="0" t="b">
         <v>0</v>
@@ -3295,9 +3415,7 @@
       <c r="J91" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K91" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K91" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="92">
       <c r="A92" s="0">
@@ -3314,8 +3432,12 @@
       <c r="D92" s="0">
         <v>23</v>
       </c>
-      <c r="F92" s="0">
-        <v>1</v>
+      <c r="E92" s="0">
+        <v>1</v>
+      </c>
+      <c r="F92" s="0"/>
+      <c r="G92" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H92" s="0" t="b">
         <v>0</v>
@@ -3326,9 +3448,7 @@
       <c r="J92" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K92" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K92" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="93">
       <c r="A93" s="0">
@@ -3345,8 +3465,12 @@
       <c r="D93" s="0">
         <v>23</v>
       </c>
-      <c r="F93" s="0">
-        <v>2</v>
+      <c r="E93" s="0">
+        <v>2</v>
+      </c>
+      <c r="F93" s="0"/>
+      <c r="G93" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H93" s="0" t="b">
         <v>0</v>
@@ -3357,9 +3481,7 @@
       <c r="J93" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K93" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K93" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="0">
@@ -3367,7 +3489,7 @@
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>RCADS-47-Y-UR</t>
+          <t>RCADS-47-Y-UR-1</t>
         </is>
       </c>
       <c r="C94" s="0">
@@ -3376,16 +3498,21 @@
       <c r="D94" s="0">
         <v>24</v>
       </c>
-      <c r="F94" s="0">
-        <v>1</v>
-      </c>
-      <c r="G94" s="0" t="inlineStr">
+      <c r="E94" s="0">
+        <v>1</v>
+      </c>
+      <c r="F94" s="0" t="inlineStr">
         <is>
           <t>incorrect item numbering after 29, missing item stem concept for item 35</t>
         </is>
       </c>
+      <c r="G94" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H94" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" s="0" t="b">
         <v>0</v>
@@ -3393,9 +3520,7 @@
       <c r="J94" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K94" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K94" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="0">
@@ -3403,7 +3528,7 @@
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>RCADS-47-CG-UR</t>
+          <t>RCADS-47-CG-UR-1</t>
         </is>
       </c>
       <c r="C95" s="0">
@@ -3412,8 +3537,12 @@
       <c r="D95" s="0">
         <v>24</v>
       </c>
-      <c r="F95" s="0">
-        <v>2</v>
+      <c r="E95" s="0">
+        <v>2</v>
+      </c>
+      <c r="F95" s="0"/>
+      <c r="G95" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H95" s="0" t="b">
         <v>0</v>
@@ -3424,9 +3553,7 @@
       <c r="J95" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K95" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K95" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="0">
@@ -3434,7 +3561,7 @@
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>RCADS-25-Y-UR</t>
+          <t>RCADS-25-Y-UR-1</t>
         </is>
       </c>
       <c r="C96" s="0">
@@ -3443,8 +3570,12 @@
       <c r="D96" s="0">
         <v>24</v>
       </c>
-      <c r="F96" s="0">
-        <v>1</v>
+      <c r="E96" s="0">
+        <v>1</v>
+      </c>
+      <c r="F96" s="0"/>
+      <c r="G96" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H96" s="0" t="b">
         <v>0</v>
@@ -3455,9 +3586,7 @@
       <c r="J96" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K96" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K96" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="97">
       <c r="A97" s="0">
@@ -3465,7 +3594,7 @@
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>RCADS-25-CG-UR</t>
+          <t>RCADS-25-CG-UR-1</t>
         </is>
       </c>
       <c r="C97" s="0">
@@ -3474,8 +3603,12 @@
       <c r="D97" s="0">
         <v>24</v>
       </c>
-      <c r="F97" s="0">
-        <v>2</v>
+      <c r="E97" s="0">
+        <v>2</v>
+      </c>
+      <c r="F97" s="0"/>
+      <c r="G97" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H97" s="0" t="b">
         <v>0</v>
@@ -3486,9 +3619,7 @@
       <c r="J97" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K97" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K97" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="0">
@@ -3505,8 +3636,12 @@
       <c r="D98" s="0">
         <v>1</v>
       </c>
-      <c r="F98" s="0">
-        <v>1</v>
+      <c r="E98" s="0">
+        <v>1</v>
+      </c>
+      <c r="F98" s="0"/>
+      <c r="G98" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H98" s="0" t="b">
         <v>0</v>
@@ -3517,9 +3652,7 @@
       <c r="J98" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K98" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K98" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="0">
@@ -3536,8 +3669,12 @@
       <c r="D99" s="0">
         <v>1</v>
       </c>
-      <c r="F99" s="0">
-        <v>2</v>
+      <c r="E99" s="0">
+        <v>2</v>
+      </c>
+      <c r="F99" s="0"/>
+      <c r="G99" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H99" s="0" t="b">
         <v>0</v>
@@ -3548,9 +3685,7 @@
       <c r="J99" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K99" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K99" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="0">
@@ -3567,8 +3702,12 @@
       <c r="D100" s="0">
         <v>21</v>
       </c>
-      <c r="F100" s="0">
-        <v>1</v>
+      <c r="E100" s="0">
+        <v>1</v>
+      </c>
+      <c r="F100" s="0"/>
+      <c r="G100" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H100" s="0" t="b">
         <v>0</v>
@@ -3579,9 +3718,7 @@
       <c r="J100" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K100" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K100" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="0">
@@ -3598,8 +3735,12 @@
       <c r="D101" s="0">
         <v>21</v>
       </c>
-      <c r="F101" s="0">
-        <v>2</v>
+      <c r="E101" s="0">
+        <v>2</v>
+      </c>
+      <c r="F101" s="0"/>
+      <c r="G101" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H101" s="0" t="b">
         <v>0</v>
@@ -3610,9 +3751,7 @@
       <c r="J101" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K101" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K101" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="0">
@@ -3629,8 +3768,12 @@
       <c r="D102" s="0">
         <v>1</v>
       </c>
-      <c r="F102" s="0">
-        <v>1</v>
+      <c r="E102" s="0">
+        <v>1</v>
+      </c>
+      <c r="F102" s="0"/>
+      <c r="G102" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H102" s="0" t="b">
         <v>0</v>
@@ -3641,9 +3784,7 @@
       <c r="J102" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K102" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K102" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="0">
@@ -3660,8 +3801,12 @@
       <c r="D103" s="0">
         <v>1</v>
       </c>
-      <c r="F103" s="0">
-        <v>2</v>
+      <c r="E103" s="0">
+        <v>2</v>
+      </c>
+      <c r="F103" s="0"/>
+      <c r="G103" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H103" s="0" t="b">
         <v>0</v>
@@ -3672,9 +3817,7 @@
       <c r="J103" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K103" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K103" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="0">
@@ -3691,16 +3834,21 @@
       <c r="D104" s="0">
         <v>21</v>
       </c>
-      <c r="F104" s="0">
-        <v>1</v>
-      </c>
-      <c r="G104" s="0" t="inlineStr">
+      <c r="E104" s="0">
+        <v>1</v>
+      </c>
+      <c r="F104" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
+      <c r="G104" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H104" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" s="0" t="b">
         <v>0</v>
@@ -3708,9 +3856,7 @@
       <c r="J104" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K104" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K104" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="0">
@@ -3727,16 +3873,21 @@
       <c r="D105" s="0">
         <v>21</v>
       </c>
-      <c r="F105" s="0">
-        <v>2</v>
-      </c>
-      <c r="G105" s="0" t="inlineStr">
+      <c r="E105" s="0">
+        <v>2</v>
+      </c>
+      <c r="F105" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
+      <c r="G105" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H105" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" s="0" t="b">
         <v>0</v>
@@ -3744,9 +3895,7 @@
       <c r="J105" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K105" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K105" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="0">
@@ -3763,14 +3912,19 @@
       <c r="D106" s="0">
         <v>1</v>
       </c>
-      <c r="F106" s="0">
-        <v>2</v>
-      </c>
-      <c r="G106" s="0" t="inlineStr">
+      <c r="E106" s="0">
+        <v>2</v>
+      </c>
+      <c r="F106" s="0" t="inlineStr">
         <is>
           <t>For autism eary intervention context</t>
         </is>
       </c>
+      <c r="G106" s="0" t="b">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H106" s="0" t="b">
         <v>0</v>
       </c>
@@ -3780,9 +3934,7 @@
       <c r="J106" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K106" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K106" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="107">
       <c r="A107" s="0">
@@ -3800,11 +3952,12 @@
         <v>1</v>
       </c>
       <c r="E107" s="0">
-        <v>9</v>
-      </c>
-      <c r="F107" s="0">
         <v>4</v>
       </c>
+      <c r="F107" s="0"/>
+      <c r="G107" s="0" t="b">
+        <v>0</v>
+      </c>
       <c r="H107" s="0" t="b">
         <v>0</v>
       </c>
@@ -3814,9 +3967,7 @@
       <c r="J107" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K107" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K107" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="108">
       <c r="A108" s="0">
@@ -3833,16 +3984,21 @@
       <c r="D108" s="0">
         <v>1</v>
       </c>
-      <c r="F108" s="0">
-        <v>1</v>
-      </c>
-      <c r="G108" s="0" t="inlineStr">
+      <c r="E108" s="0">
+        <v>1</v>
+      </c>
+      <c r="F108" s="0" t="inlineStr">
         <is>
           <t>Manasi Kumar MMA derivative</t>
         </is>
       </c>
+      <c r="G108" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H108" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" s="0" t="b">
         <v>0</v>
@@ -3850,9 +4006,7 @@
       <c r="J108" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K108" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K108" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="109">
       <c r="A109" s="0">
@@ -3869,16 +4023,21 @@
       <c r="D109" s="0">
         <v>26</v>
       </c>
-      <c r="F109" s="0">
-        <v>1</v>
-      </c>
-      <c r="G109" s="0" t="inlineStr">
+      <c r="E109" s="0">
+        <v>1</v>
+      </c>
+      <c r="F109" s="0" t="inlineStr">
         <is>
           <t>Manasi Kumar MMA derivative 2</t>
         </is>
       </c>
+      <c r="G109" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H109" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" s="0" t="b">
         <v>0</v>
@@ -3886,9 +4045,7 @@
       <c r="J109" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K109" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K109" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="110">
       <c r="A110" s="0">
@@ -3905,8 +4062,12 @@
       <c r="D110" s="0">
         <v>27</v>
       </c>
-      <c r="F110" s="0">
-        <v>1</v>
+      <c r="E110" s="0">
+        <v>1</v>
+      </c>
+      <c r="F110" s="0"/>
+      <c r="G110" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H110" s="0" t="b">
         <v>0</v>
@@ -3917,9 +4078,7 @@
       <c r="J110" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K110" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K110" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="0">
@@ -3936,8 +4095,12 @@
       <c r="D111" s="0">
         <v>27</v>
       </c>
-      <c r="F111" s="0">
-        <v>2</v>
+      <c r="E111" s="0">
+        <v>2</v>
+      </c>
+      <c r="F111" s="0"/>
+      <c r="G111" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H111" s="0" t="b">
         <v>0</v>
@@ -3948,9 +4111,7 @@
       <c r="J111" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K111" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K111" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="0">
@@ -3967,8 +4128,12 @@
       <c r="D112" s="0">
         <v>13</v>
       </c>
-      <c r="F112" s="0">
-        <v>1</v>
+      <c r="E112" s="0">
+        <v>1</v>
+      </c>
+      <c r="F112" s="0"/>
+      <c r="G112" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H112" s="0" t="b">
         <v>0</v>
@@ -3979,9 +4144,7 @@
       <c r="J112" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K112" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K112" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="0">
@@ -3998,8 +4161,12 @@
       <c r="D113" s="0">
         <v>13</v>
       </c>
-      <c r="F113" s="0">
-        <v>2</v>
+      <c r="E113" s="0">
+        <v>2</v>
+      </c>
+      <c r="F113" s="0"/>
+      <c r="G113" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H113" s="0" t="b">
         <v>0</v>
@@ -4010,9 +4177,7 @@
       <c r="J113" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K113" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K113" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="0">
@@ -4029,16 +4194,21 @@
       <c r="D114" s="0">
         <v>8</v>
       </c>
-      <c r="F114" s="0">
-        <v>1</v>
-      </c>
-      <c r="G114" s="0" t="inlineStr">
+      <c r="E114" s="0">
+        <v>1</v>
+      </c>
+      <c r="F114" s="0" t="inlineStr">
         <is>
           <t>Boustani update</t>
         </is>
       </c>
+      <c r="G114" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H114" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" s="0" t="b">
         <v>0</v>
@@ -4046,9 +4216,7 @@
       <c r="J114" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K114" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K114" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="0">
@@ -4065,16 +4233,21 @@
       <c r="D115" s="0">
         <v>16</v>
       </c>
-      <c r="F115" s="0">
-        <v>1</v>
-      </c>
-      <c r="G115" s="0" t="inlineStr">
+      <c r="E115" s="0">
+        <v>1</v>
+      </c>
+      <c r="F115" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
+      <c r="G115" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H115" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" s="0" t="b">
         <v>0</v>
@@ -4082,9 +4255,7 @@
       <c r="J115" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K115" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K115" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="116">
       <c r="A116" s="0">
@@ -4101,16 +4272,21 @@
       <c r="D116" s="0">
         <v>16</v>
       </c>
-      <c r="F116" s="0">
-        <v>2</v>
-      </c>
-      <c r="G116" s="0" t="inlineStr">
+      <c r="E116" s="0">
+        <v>2</v>
+      </c>
+      <c r="F116" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
+      <c r="G116" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H116" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" s="0" t="b">
         <v>0</v>
@@ -4118,9 +4294,7 @@
       <c r="J116" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K116" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K116" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="117">
       <c r="A117" s="0">
@@ -4137,16 +4311,21 @@
       <c r="D117" s="0">
         <v>25</v>
       </c>
-      <c r="F117" s="0">
-        <v>1</v>
-      </c>
-      <c r="G117" s="0" t="inlineStr">
+      <c r="E117" s="0">
+        <v>1</v>
+      </c>
+      <c r="F117" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
+      <c r="G117" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H117" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" s="0" t="b">
         <v>0</v>
@@ -4154,9 +4333,7 @@
       <c r="J117" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K117" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K117" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="118">
       <c r="A118" s="0">
@@ -4173,26 +4350,29 @@
       <c r="D118" s="0">
         <v>25</v>
       </c>
-      <c r="F118" s="0">
-        <v>2</v>
-      </c>
-      <c r="G118" s="0" t="inlineStr">
+      <c r="E118" s="0">
+        <v>2</v>
+      </c>
+      <c r="F118" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G118" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H118" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J118" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K118" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K118" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="119">
       <c r="A119" s="0">
@@ -4209,16 +4389,21 @@
       <c r="D119" s="0">
         <v>25</v>
       </c>
-      <c r="F119" s="0">
-        <v>1</v>
-      </c>
-      <c r="G119" s="0" t="inlineStr">
+      <c r="E119" s="0">
+        <v>1</v>
+      </c>
+      <c r="F119" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
+      <c r="G119" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H119" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" s="0" t="b">
         <v>0</v>
@@ -4226,9 +4411,7 @@
       <c r="J119" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K119" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K119" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="0">
@@ -4245,26 +4428,29 @@
       <c r="D120" s="0">
         <v>25</v>
       </c>
-      <c r="F120" s="0">
-        <v>2</v>
-      </c>
-      <c r="G120" s="0" t="inlineStr">
+      <c r="E120" s="0">
+        <v>2</v>
+      </c>
+      <c r="F120" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G120" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H120" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J120" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K120" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K120" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="0">
@@ -4281,8 +4467,12 @@
       <c r="D121" s="0">
         <v>29</v>
       </c>
-      <c r="F121" s="0">
-        <v>1</v>
+      <c r="E121" s="0">
+        <v>1</v>
+      </c>
+      <c r="F121" s="0"/>
+      <c r="G121" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H121" s="0" t="b">
         <v>0</v>
@@ -4293,9 +4483,7 @@
       <c r="J121" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K121" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K121" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="0">
@@ -4312,26 +4500,29 @@
       <c r="D122" s="0">
         <v>29</v>
       </c>
-      <c r="F122" s="0">
-        <v>2</v>
-      </c>
-      <c r="G122" s="0" t="inlineStr">
+      <c r="E122" s="0">
+        <v>2</v>
+      </c>
+      <c r="F122" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G122" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H122" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J122" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K122" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K122" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="0">
@@ -4348,26 +4539,29 @@
       <c r="D123" s="0">
         <v>29</v>
       </c>
-      <c r="F123" s="0">
-        <v>1</v>
-      </c>
-      <c r="G123" s="0" t="inlineStr">
+      <c r="E123" s="0">
+        <v>1</v>
+      </c>
+      <c r="F123" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G123" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H123" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I123" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J123" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K123" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K123" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="0">
@@ -4384,26 +4578,29 @@
       <c r="D124" s="0">
         <v>29</v>
       </c>
-      <c r="F124" s="0">
-        <v>2</v>
-      </c>
-      <c r="G124" s="0" t="inlineStr">
+      <c r="E124" s="0">
+        <v>2</v>
+      </c>
+      <c r="F124" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G124" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H124" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J124" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K124" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K124" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="0">
@@ -4420,26 +4617,29 @@
       <c r="D125" s="0">
         <v>28</v>
       </c>
-      <c r="F125" s="0">
-        <v>1</v>
-      </c>
-      <c r="G125" s="0" t="inlineStr">
+      <c r="E125" s="0">
+        <v>1</v>
+      </c>
+      <c r="F125" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G125" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H125" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J125" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K125" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K125" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="0">
@@ -4456,14 +4656,19 @@
       <c r="D126" s="0">
         <v>28</v>
       </c>
-      <c r="F126" s="0">
-        <v>2</v>
-      </c>
-      <c r="G126" s="0" t="inlineStr">
+      <c r="E126" s="0">
+        <v>2</v>
+      </c>
+      <c r="F126" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G126" s="0" t="b">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H126" s="0" t="b">
         <v>0</v>
       </c>
@@ -4471,11 +4676,9 @@
         <v>0</v>
       </c>
       <c r="J126" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K126" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K126" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="127">
       <c r="A127" s="0">
@@ -4492,16 +4695,21 @@
       <c r="D127" s="0">
         <v>28</v>
       </c>
-      <c r="F127" s="0">
-        <v>1</v>
-      </c>
-      <c r="G127" s="0" t="inlineStr">
+      <c r="E127" s="0">
+        <v>1</v>
+      </c>
+      <c r="F127" s="0" t="inlineStr">
         <is>
           <t>No items</t>
         </is>
       </c>
+      <c r="G127" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H127" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" s="0" t="b">
         <v>0</v>
@@ -4509,9 +4717,7 @@
       <c r="J127" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K127" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K127" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="0">
@@ -4528,26 +4734,29 @@
       <c r="D128" s="0">
         <v>28</v>
       </c>
-      <c r="F128" s="0">
-        <v>2</v>
-      </c>
-      <c r="G128" s="0" t="inlineStr">
+      <c r="E128" s="0">
+        <v>2</v>
+      </c>
+      <c r="F128" s="0" t="inlineStr">
         <is>
           <t>Not yet generated</t>
         </is>
       </c>
+      <c r="G128" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H128" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J128" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K128" s="0" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K128" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="0">
@@ -4564,8 +4773,12 @@
       <c r="D129" s="0">
         <v>16</v>
       </c>
-      <c r="F129" s="0">
-        <v>1</v>
+      <c r="E129" s="0">
+        <v>1</v>
+      </c>
+      <c r="F129" s="0"/>
+      <c r="G129" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H129" s="0" t="b">
         <v>0</v>
@@ -4576,9 +4789,7 @@
       <c r="J129" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K129" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K129" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="0">
@@ -4595,8 +4806,12 @@
       <c r="D130" s="0">
         <v>16</v>
       </c>
-      <c r="F130" s="0">
-        <v>2</v>
+      <c r="E130" s="0">
+        <v>2</v>
+      </c>
+      <c r="F130" s="0"/>
+      <c r="G130" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H130" s="0" t="b">
         <v>0</v>
@@ -4607,9 +4822,7 @@
       <c r="J130" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K130" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K130" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="0">
@@ -4626,8 +4839,12 @@
       <c r="D131" s="0">
         <v>22</v>
       </c>
-      <c r="F131" s="0">
-        <v>2</v>
+      <c r="E131" s="0">
+        <v>2</v>
+      </c>
+      <c r="F131" s="0"/>
+      <c r="G131" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H131" s="0" t="b">
         <v>0</v>
@@ -4638,9 +4855,7 @@
       <c r="J131" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K131" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K131" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="0">
@@ -4657,9 +4872,13 @@
       <c r="D132" s="0">
         <v>1</v>
       </c>
-      <c r="F132" s="0">
+      <c r="E132" s="0">
         <v>4</v>
       </c>
+      <c r="F132" s="0"/>
+      <c r="G132" s="0" t="b">
+        <v>0</v>
+      </c>
       <c r="H132" s="0" t="b">
         <v>0</v>
       </c>
@@ -4669,9 +4888,7 @@
       <c r="J132" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K132" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K132" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="0">
@@ -4688,16 +4905,21 @@
       <c r="D133" s="0">
         <v>31</v>
       </c>
-      <c r="F133" s="0">
-        <v>1</v>
-      </c>
-      <c r="G133" s="0" t="inlineStr">
+      <c r="E133" s="0">
+        <v>1</v>
+      </c>
+      <c r="F133" s="0" t="inlineStr">
         <is>
           <t>New translator found spelling mistakes and said that this version has complex/formal words that are not suitable for laypersons across all of India</t>
         </is>
       </c>
+      <c r="G133" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H133" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="0" t="b">
         <v>0</v>
@@ -4705,9 +4927,7 @@
       <c r="J133" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K133" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K133" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="0">
@@ -4724,21 +4944,23 @@
       <c r="D134" s="0">
         <v>31</v>
       </c>
-      <c r="F134" s="0">
-        <v>1</v>
+      <c r="E134" s="0">
+        <v>1</v>
+      </c>
+      <c r="F134" s="0"/>
+      <c r="G134" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H134" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I134" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J134" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K134" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K134" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="0">
@@ -4755,21 +4977,23 @@
       <c r="D135" s="0">
         <v>31</v>
       </c>
-      <c r="F135" s="0">
-        <v>1</v>
+      <c r="E135" s="0">
+        <v>1</v>
+      </c>
+      <c r="F135" s="0"/>
+      <c r="G135" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H135" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K135" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K135" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="0">
@@ -4786,21 +5010,23 @@
       <c r="D136" s="0">
         <v>31</v>
       </c>
-      <c r="F136" s="0">
-        <v>1</v>
+      <c r="E136" s="0">
+        <v>1</v>
+      </c>
+      <c r="F136" s="0"/>
+      <c r="G136" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H136" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I136" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J136" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K136" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K136" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="0">
@@ -4817,21 +5043,23 @@
       <c r="D137" s="0">
         <v>31</v>
       </c>
-      <c r="F137" s="0">
-        <v>1</v>
+      <c r="E137" s="0">
+        <v>1</v>
+      </c>
+      <c r="F137" s="0"/>
+      <c r="G137" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H137" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J137" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K137" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K137" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="0">
@@ -4848,21 +5076,23 @@
       <c r="D138" s="0">
         <v>32</v>
       </c>
-      <c r="F138" s="0">
-        <v>1</v>
+      <c r="E138" s="0">
+        <v>1</v>
+      </c>
+      <c r="F138" s="0"/>
+      <c r="G138" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H138" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I138" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J138" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K138" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K138" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="0">
@@ -4879,21 +5109,23 @@
       <c r="D139" s="0">
         <v>32</v>
       </c>
-      <c r="F139" s="0">
-        <v>2</v>
+      <c r="E139" s="0">
+        <v>2</v>
+      </c>
+      <c r="F139" s="0"/>
+      <c r="G139" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H139" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K139" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K139" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="0">
@@ -4910,21 +5142,23 @@
       <c r="D140" s="0">
         <v>32</v>
       </c>
-      <c r="F140" s="0">
-        <v>1</v>
+      <c r="E140" s="0">
+        <v>1</v>
+      </c>
+      <c r="F140" s="0"/>
+      <c r="G140" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H140" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J140" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K140" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K140" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="0">
@@ -4941,21 +5175,23 @@
       <c r="D141" s="0">
         <v>32</v>
       </c>
-      <c r="F141" s="0">
-        <v>2</v>
+      <c r="E141" s="0">
+        <v>2</v>
+      </c>
+      <c r="F141" s="0"/>
+      <c r="G141" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H141" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I141" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K141" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K141" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="0">
@@ -4972,8 +5208,12 @@
       <c r="D142" s="0">
         <v>27</v>
       </c>
-      <c r="F142" s="0">
-        <v>1</v>
+      <c r="E142" s="0">
+        <v>1</v>
+      </c>
+      <c r="F142" s="0"/>
+      <c r="G142" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H142" s="0" t="b">
         <v>0</v>
@@ -4984,9 +5224,7 @@
       <c r="J142" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K142" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K142" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="0">
@@ -5003,8 +5241,12 @@
       <c r="D143" s="0">
         <v>27</v>
       </c>
-      <c r="F143" s="0">
-        <v>1</v>
+      <c r="E143" s="0">
+        <v>1</v>
+      </c>
+      <c r="F143" s="0"/>
+      <c r="G143" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H143" s="0" t="b">
         <v>0</v>
@@ -5015,9 +5257,7 @@
       <c r="J143" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K143" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K143" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="0">
@@ -5034,21 +5274,23 @@
       <c r="D144" s="0">
         <v>38</v>
       </c>
-      <c r="F144" s="0">
-        <v>1</v>
+      <c r="E144" s="0">
+        <v>1</v>
+      </c>
+      <c r="F144" s="0"/>
+      <c r="G144" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H144" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K144" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K144" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="0">
@@ -5065,16 +5307,21 @@
       <c r="D145" s="0">
         <v>8</v>
       </c>
-      <c r="F145" s="0">
-        <v>2</v>
-      </c>
-      <c r="G145" s="0" t="inlineStr">
+      <c r="E145" s="0">
+        <v>2</v>
+      </c>
+      <c r="F145" s="0" t="inlineStr">
         <is>
           <t>Dayer 2023 - unknown if canadian or france french- google team?</t>
         </is>
       </c>
+      <c r="G145" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H145" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" s="0" t="b">
         <v>0</v>
@@ -5082,9 +5329,7 @@
       <c r="J145" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K145" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K145" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="0">
@@ -5101,16 +5346,21 @@
       <c r="D146" s="0">
         <v>8</v>
       </c>
-      <c r="F146" s="0">
-        <v>2</v>
-      </c>
-      <c r="G146" s="0" t="inlineStr">
+      <c r="E146" s="0">
+        <v>2</v>
+      </c>
+      <c r="F146" s="0" t="inlineStr">
         <is>
           <t>Unauthorized version from NHS (UK)</t>
         </is>
       </c>
+      <c r="G146" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H146" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146" s="0" t="b">
         <v>0</v>
@@ -5118,9 +5368,7 @@
       <c r="J146" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K146" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K146" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="0">
@@ -5137,16 +5385,21 @@
       <c r="D147" s="0">
         <v>8</v>
       </c>
-      <c r="F147" s="0">
-        <v>1</v>
-      </c>
-      <c r="G147" s="0" t="inlineStr">
+      <c r="E147" s="0">
+        <v>1</v>
+      </c>
+      <c r="F147" s="0" t="inlineStr">
         <is>
           <t>Boustani update</t>
         </is>
       </c>
+      <c r="G147" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H147" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147" s="0" t="b">
         <v>0</v>
@@ -5154,9 +5407,7 @@
       <c r="J147" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K147" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K147" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="0">
@@ -5173,21 +5424,23 @@
       <c r="D148" s="0">
         <v>38</v>
       </c>
-      <c r="F148" s="0">
-        <v>2</v>
+      <c r="E148" s="0">
+        <v>2</v>
+      </c>
+      <c r="F148" s="0"/>
+      <c r="G148" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H148" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K148" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K148" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="0">
@@ -5204,21 +5457,23 @@
       <c r="D149" s="0">
         <v>38</v>
       </c>
-      <c r="F149" s="0">
-        <v>1</v>
+      <c r="E149" s="0">
+        <v>1</v>
+      </c>
+      <c r="F149" s="0"/>
+      <c r="G149" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H149" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J149" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K149" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K149" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="0">
@@ -5235,21 +5490,23 @@
       <c r="D150" s="0">
         <v>38</v>
       </c>
-      <c r="F150" s="0">
-        <v>2</v>
+      <c r="E150" s="0">
+        <v>2</v>
+      </c>
+      <c r="F150" s="0"/>
+      <c r="G150" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H150" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I150" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K150" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K150" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="0">
@@ -5267,18 +5524,20 @@
         <v>8</v>
       </c>
       <c r="E151" s="0">
-        <v>8</v>
-      </c>
-      <c r="F151" s="0">
-        <v>1</v>
-      </c>
-      <c r="G151" s="0" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="F151" s="0" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
+      <c r="G151" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H151" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151" s="0" t="b">
         <v>0</v>
@@ -5286,9 +5545,7 @@
       <c r="J151" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K151" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K151" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="0">
@@ -5306,18 +5563,20 @@
         <v>8</v>
       </c>
       <c r="E152" s="0">
-        <v>4</v>
-      </c>
-      <c r="F152" s="0">
-        <v>2</v>
-      </c>
-      <c r="G152" s="0" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="F152" s="0" t="inlineStr">
         <is>
           <t>Boustani update, combined versions 1 and 2 while consulting youth version 1</t>
         </is>
       </c>
+      <c r="G152" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H152" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I152" s="0" t="b">
         <v>0</v>
@@ -5325,9 +5584,7 @@
       <c r="J152" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K152" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K152" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="0">
@@ -5345,18 +5602,20 @@
         <v>8</v>
       </c>
       <c r="E153" s="0">
-        <v>8</v>
-      </c>
-      <c r="F153" s="0">
-        <v>1</v>
-      </c>
-      <c r="G153" s="0" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="F153" s="0" t="inlineStr">
         <is>
           <t>No items; Unauthorized Canadian changes</t>
         </is>
       </c>
+      <c r="G153" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H153" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153" s="0" t="b">
         <v>0</v>
@@ -5364,9 +5623,7 @@
       <c r="J153" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K153" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K153" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="0">
@@ -5384,18 +5641,20 @@
         <v>8</v>
       </c>
       <c r="E154" s="0">
-        <v>8</v>
-      </c>
-      <c r="F154" s="0">
-        <v>2</v>
-      </c>
-      <c r="G154" s="0" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="F154" s="0" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
+      <c r="G154" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H154" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154" s="0" t="b">
         <v>0</v>
@@ -5403,9 +5662,7 @@
       <c r="J154" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K154" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K154" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="155">
       <c r="A155" s="0">
@@ -5422,8 +5679,12 @@
       <c r="D155" s="0">
         <v>36</v>
       </c>
-      <c r="F155" s="0">
-        <v>1</v>
+      <c r="E155" s="0">
+        <v>1</v>
+      </c>
+      <c r="F155" s="0"/>
+      <c r="G155" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H155" s="0" t="b">
         <v>0</v>
@@ -5434,9 +5695,7 @@
       <c r="J155" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K155" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K155" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="156">
       <c r="A156" s="0">
@@ -5453,8 +5712,12 @@
       <c r="D156" s="0">
         <v>36</v>
       </c>
-      <c r="F156" s="0">
-        <v>2</v>
+      <c r="E156" s="0">
+        <v>2</v>
+      </c>
+      <c r="F156" s="0"/>
+      <c r="G156" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H156" s="0" t="b">
         <v>0</v>
@@ -5465,9 +5728,7 @@
       <c r="J156" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K156" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K156" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="157">
       <c r="A157" s="0">
@@ -5484,21 +5745,23 @@
       <c r="D157" s="0">
         <v>1</v>
       </c>
-      <c r="F157" s="0">
-        <v>2</v>
+      <c r="E157" s="0">
+        <v>2</v>
+      </c>
+      <c r="F157" s="0"/>
+      <c r="G157" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H157" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I157" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J157" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K157" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K157" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="0">
@@ -5515,21 +5778,23 @@
       <c r="D158" s="0">
         <v>1</v>
       </c>
-      <c r="F158" s="0">
-        <v>2</v>
+      <c r="E158" s="0">
+        <v>2</v>
+      </c>
+      <c r="F158" s="0"/>
+      <c r="G158" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H158" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I158" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K158" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K158" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="0">
@@ -5546,21 +5811,23 @@
       <c r="D159" s="0">
         <v>34</v>
       </c>
-      <c r="F159" s="0">
-        <v>1</v>
+      <c r="E159" s="0">
+        <v>1</v>
+      </c>
+      <c r="F159" s="0"/>
+      <c r="G159" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H159" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J159" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K159" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K159" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="0">
@@ -5577,21 +5844,23 @@
       <c r="D160" s="0">
         <v>34</v>
       </c>
-      <c r="F160" s="0">
-        <v>2</v>
+      <c r="E160" s="0">
+        <v>2</v>
+      </c>
+      <c r="F160" s="0"/>
+      <c r="G160" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H160" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J160" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K160" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K160" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="0">
@@ -5608,26 +5877,29 @@
       <c r="D161" s="0">
         <v>34</v>
       </c>
-      <c r="F161" s="0">
-        <v>1</v>
-      </c>
-      <c r="G161" s="0" t="inlineStr">
+      <c r="E161" s="0">
+        <v>1</v>
+      </c>
+      <c r="F161" s="0" t="inlineStr">
         <is>
           <t>Inconsistent codebook response option</t>
         </is>
       </c>
+      <c r="G161" s="0" t="b">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H161" s="0" t="b">
         <v>1</v>
       </c>
       <c r="I161" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K161" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K161" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="0">
@@ -5644,21 +5916,23 @@
       <c r="D162" s="0">
         <v>34</v>
       </c>
-      <c r="F162" s="0">
-        <v>2</v>
+      <c r="E162" s="0">
+        <v>2</v>
+      </c>
+      <c r="F162" s="0"/>
+      <c r="G162" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H162" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K162" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K162" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="0">
@@ -5675,21 +5949,23 @@
       <c r="D163" s="0">
         <v>39</v>
       </c>
-      <c r="F163" s="0">
-        <v>1</v>
+      <c r="E163" s="0">
+        <v>1</v>
+      </c>
+      <c r="F163" s="0"/>
+      <c r="G163" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H163" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J163" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K163" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K163" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="0">
@@ -5706,21 +5982,23 @@
       <c r="D164" s="0">
         <v>39</v>
       </c>
-      <c r="F164" s="0">
-        <v>2</v>
+      <c r="E164" s="0">
+        <v>2</v>
+      </c>
+      <c r="F164" s="0"/>
+      <c r="G164" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H164" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K164" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K164" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="0">
@@ -5737,21 +6015,23 @@
       <c r="D165" s="0">
         <v>39</v>
       </c>
-      <c r="F165" s="0">
-        <v>1</v>
+      <c r="E165" s="0">
+        <v>1</v>
+      </c>
+      <c r="F165" s="0"/>
+      <c r="G165" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H165" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J165" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K165" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K165" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="0">
@@ -5768,21 +6048,23 @@
       <c r="D166" s="0">
         <v>39</v>
       </c>
-      <c r="F166" s="0">
-        <v>2</v>
+      <c r="E166" s="0">
+        <v>2</v>
+      </c>
+      <c r="F166" s="0"/>
+      <c r="G166" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H166" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J166" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K166" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K166" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="0">
@@ -5799,21 +6081,23 @@
       <c r="D167" s="0">
         <v>40</v>
       </c>
-      <c r="F167" s="0">
-        <v>1</v>
+      <c r="E167" s="0">
+        <v>1</v>
+      </c>
+      <c r="F167" s="0"/>
+      <c r="G167" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H167" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K167" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K167" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="0">
@@ -5830,21 +6114,23 @@
       <c r="D168" s="0">
         <v>40</v>
       </c>
-      <c r="F168" s="0">
-        <v>2</v>
+      <c r="E168" s="0">
+        <v>2</v>
+      </c>
+      <c r="F168" s="0"/>
+      <c r="G168" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H168" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K168" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K168" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="0">
@@ -5861,21 +6147,23 @@
       <c r="D169" s="0">
         <v>40</v>
       </c>
-      <c r="F169" s="0">
-        <v>1</v>
+      <c r="E169" s="0">
+        <v>1</v>
+      </c>
+      <c r="F169" s="0"/>
+      <c r="G169" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H169" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K169" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K169" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="0">
@@ -5892,21 +6180,23 @@
       <c r="D170" s="0">
         <v>40</v>
       </c>
-      <c r="F170" s="0">
-        <v>2</v>
+      <c r="E170" s="0">
+        <v>2</v>
+      </c>
+      <c r="F170" s="0"/>
+      <c r="G170" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H170" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I170" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K170" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K170" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="0">
@@ -5923,8 +6213,12 @@
       <c r="D171" s="0">
         <v>36</v>
       </c>
-      <c r="F171" s="0">
-        <v>1</v>
+      <c r="E171" s="0">
+        <v>1</v>
+      </c>
+      <c r="F171" s="0"/>
+      <c r="G171" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H171" s="0" t="b">
         <v>0</v>
@@ -5935,9 +6229,7 @@
       <c r="J171" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K171" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K171" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="0">
@@ -5954,8 +6246,12 @@
       <c r="D172" s="0">
         <v>36</v>
       </c>
-      <c r="F172" s="0">
-        <v>2</v>
+      <c r="E172" s="0">
+        <v>2</v>
+      </c>
+      <c r="F172" s="0"/>
+      <c r="G172" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H172" s="0" t="b">
         <v>0</v>
@@ -5966,9 +6262,7 @@
       <c r="J172" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K172" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K172" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="0">
@@ -5985,21 +6279,23 @@
       <c r="D173" s="0">
         <v>41</v>
       </c>
-      <c r="F173" s="0">
-        <v>1</v>
+      <c r="E173" s="0">
+        <v>1</v>
+      </c>
+      <c r="F173" s="0"/>
+      <c r="G173" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H173" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J173" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K173" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K173" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="0">
@@ -6016,21 +6312,23 @@
       <c r="D174" s="0">
         <v>41</v>
       </c>
-      <c r="F174" s="0">
-        <v>2</v>
+      <c r="E174" s="0">
+        <v>2</v>
+      </c>
+      <c r="F174" s="0"/>
+      <c r="G174" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H174" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I174" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J174" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K174" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K174" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="0">
@@ -6047,21 +6345,23 @@
       <c r="D175" s="0">
         <v>41</v>
       </c>
-      <c r="F175" s="0">
-        <v>1</v>
+      <c r="E175" s="0">
+        <v>1</v>
+      </c>
+      <c r="F175" s="0"/>
+      <c r="G175" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H175" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I175" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J175" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K175" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K175" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="0">
@@ -6078,21 +6378,23 @@
       <c r="D176" s="0">
         <v>41</v>
       </c>
-      <c r="F176" s="0">
-        <v>2</v>
+      <c r="E176" s="0">
+        <v>2</v>
+      </c>
+      <c r="F176" s="0"/>
+      <c r="G176" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H176" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I176" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J176" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K176" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K176" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="0">
@@ -6109,21 +6411,23 @@
       <c r="D177" s="0">
         <v>34</v>
       </c>
-      <c r="F177" s="0">
-        <v>1</v>
+      <c r="E177" s="0">
+        <v>1</v>
+      </c>
+      <c r="F177" s="0"/>
+      <c r="G177" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H177" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I177" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J177" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K177" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K177" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="0">
@@ -6140,21 +6444,23 @@
       <c r="D178" s="0">
         <v>42</v>
       </c>
-      <c r="F178" s="0">
-        <v>1</v>
+      <c r="E178" s="0">
+        <v>1</v>
+      </c>
+      <c r="F178" s="0"/>
+      <c r="G178" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H178" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I178" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J178" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K178" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K178" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="0">
@@ -6171,21 +6477,23 @@
       <c r="D179" s="0">
         <v>42</v>
       </c>
-      <c r="F179" s="0">
-        <v>2</v>
+      <c r="E179" s="0">
+        <v>2</v>
+      </c>
+      <c r="F179" s="0"/>
+      <c r="G179" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H179" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I179" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J179" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K179" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K179" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="0">
@@ -6202,21 +6510,23 @@
       <c r="D180" s="0">
         <v>42</v>
       </c>
-      <c r="F180" s="0">
-        <v>1</v>
+      <c r="E180" s="0">
+        <v>1</v>
+      </c>
+      <c r="F180" s="0"/>
+      <c r="G180" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H180" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I180" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J180" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K180" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K180" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="0">
@@ -6233,21 +6543,23 @@
       <c r="D181" s="0">
         <v>42</v>
       </c>
-      <c r="F181" s="0">
-        <v>2</v>
+      <c r="E181" s="0">
+        <v>2</v>
+      </c>
+      <c r="F181" s="0"/>
+      <c r="G181" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H181" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I181" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J181" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K181" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K181" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="0">
@@ -6255,7 +6567,7 @@
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>PHQ-9-A-EN-US</t>
+          <t>PHQ-9-A-EN-US-HK</t>
         </is>
       </c>
       <c r="C182" s="0">
@@ -6265,11 +6577,12 @@
         <v>1</v>
       </c>
       <c r="E182" s="0">
-        <v>1</v>
-      </c>
-      <c r="F182" s="0">
         <v>4</v>
       </c>
+      <c r="F182" s="0"/>
+      <c r="G182" s="0" t="b">
+        <v>0</v>
+      </c>
       <c r="H182" s="0" t="b">
         <v>0</v>
       </c>
@@ -6279,9 +6592,7 @@
       <c r="J182" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K182" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K182" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="0">
@@ -6299,11 +6610,12 @@
         <v>1</v>
       </c>
       <c r="E183" s="0">
-        <v>9</v>
-      </c>
-      <c r="F183" s="0">
         <v>4</v>
       </c>
+      <c r="F183" s="0"/>
+      <c r="G183" s="0" t="b">
+        <v>0</v>
+      </c>
       <c r="H183" s="0" t="b">
         <v>0</v>
       </c>
@@ -6313,9 +6625,7 @@
       <c r="J183" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K183" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K183" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="0">
@@ -6333,11 +6643,12 @@
         <v>1</v>
       </c>
       <c r="E184" s="0">
-        <v>8</v>
-      </c>
-      <c r="F184" s="0">
         <v>4</v>
       </c>
+      <c r="F184" s="0"/>
+      <c r="G184" s="0" t="b">
+        <v>0</v>
+      </c>
       <c r="H184" s="0" t="b">
         <v>0</v>
       </c>
@@ -6347,9 +6658,7 @@
       <c r="J184" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K184" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K184" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="0">
@@ -6367,11 +6676,12 @@
         <v>1</v>
       </c>
       <c r="E185" s="0">
-        <v>10</v>
-      </c>
-      <c r="F185" s="0">
         <v>4</v>
       </c>
+      <c r="F185" s="0"/>
+      <c r="G185" s="0" t="b">
+        <v>0</v>
+      </c>
       <c r="H185" s="0" t="b">
         <v>0</v>
       </c>
@@ -6381,9 +6691,7 @@
       <c r="J185" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K185" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K185" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="0">
@@ -6401,11 +6709,12 @@
         <v>1</v>
       </c>
       <c r="E186" s="0">
-        <v>10</v>
-      </c>
-      <c r="F186" s="0">
         <v>4</v>
       </c>
+      <c r="F186" s="0"/>
+      <c r="G186" s="0" t="b">
+        <v>0</v>
+      </c>
       <c r="H186" s="0" t="b">
         <v>0</v>
       </c>
@@ -6415,30 +6724,19 @@
       <c r="J186" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K186" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K186" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="0">
         <v>186</v>
       </c>
-      <c r="B187" s="0" t="inlineStr">
-        <is>
-          <t>PHQ-9-A-EN-HK</t>
-        </is>
-      </c>
-      <c r="C187" s="0">
-        <v>4</v>
-      </c>
-      <c r="D187" s="0">
-        <v>1</v>
-      </c>
-      <c r="E187" s="0">
-        <v>11</v>
-      </c>
-      <c r="F187" s="0">
-        <v>4</v>
+      <c r="B187" s="0" t="inlineStr"/>
+      <c r="C187" s="0"/>
+      <c r="D187" s="0"/>
+      <c r="E187" s="0"/>
+      <c r="F187" s="0"/>
+      <c r="G187" s="0" t="b">
+        <v>0</v>
       </c>
       <c r="H187" s="0" t="b">
         <v>0</v>
@@ -6449,9 +6747,7 @@
       <c r="J187" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K187" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K187" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="0">
@@ -6468,9 +6764,13 @@
       <c r="D188" s="0">
         <v>1</v>
       </c>
-      <c r="F188" s="0">
+      <c r="E188" s="0">
         <v>4</v>
       </c>
+      <c r="F188" s="0"/>
+      <c r="G188" s="0" t="b">
+        <v>0</v>
+      </c>
       <c r="H188" s="0" t="b">
         <v>0</v>
       </c>
@@ -6480,9 +6780,7 @@
       <c r="J188" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K188" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="K188" s="0" t="b"/>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="0">
@@ -6502,19 +6800,137 @@
       <c r="E189" s="0">
         <v>4</v>
       </c>
-      <c r="F189" s="0">
+      <c r="F189" s="0"/>
+      <c r="G189" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H189" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I189" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J189" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K189" s="0" t="b"/>
+    </row>
+    <row outlineLevel="0" r="190">
+      <c r="A190" s="0">
+        <v>189</v>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-Y-UR-2</t>
+        </is>
+      </c>
+      <c r="G190" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H190" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I190" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J190" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="191">
+      <c r="A191" s="0">
+        <v>190</v>
+      </c>
+      <c r="B191" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-CG-UR-2</t>
+        </is>
+      </c>
+      <c r="G191" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H191" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I191" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J191" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="192">
+      <c r="A192" s="0">
+        <v>191</v>
+      </c>
+      <c r="B192" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-Y-SD-1</t>
+        </is>
+      </c>
+      <c r="G192" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H192" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I192" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J192" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="193">
+      <c r="A193" s="0">
+        <v>192</v>
+      </c>
+      <c r="B193" s="0" t="inlineStr">
+        <is>
+          <t>RCADS-25-CG-SD-1</t>
+        </is>
+      </c>
+      <c r="G193" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H193" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I193" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J193" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="194">
+      <c r="A194" s="0">
+        <v>193</v>
+      </c>
+      <c r="B194" s="0" t="inlineStr">
+        <is>
+          <t>PHQ-9-A-EN-IN</t>
+        </is>
+      </c>
+      <c r="C194" s="0">
         <v>4</v>
       </c>
-      <c r="H189" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="I189" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J189" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K189" s="0" t="b">
+      <c r="D194" s="0">
+        <v>1</v>
+      </c>
+      <c r="E194" s="0">
+        <v>4</v>
+      </c>
+      <c r="G194" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H194" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I194" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J194" s="0" t="b">
         <v>0</v>
       </c>
     </row>
